--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="fistpayment" sheetId="1" r:id="rId1"/>
+    <sheet name="firstpayment" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,48 +26,12 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-条件配置表中的ID
-ID_值</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>序列ID</t>
   </si>
   <si>
-    <t>激活条件</t>
-  </si>
-  <si>
     <t>购买金额</t>
   </si>
   <si>
@@ -83,18 +47,12 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
-  </si>
-  <si>
     <t>map&lt;int{_}long&gt;{;}</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>condition</t>
-  </si>
-  <si>
     <t>money</t>
   </si>
   <si>
@@ -105,9 +63,6 @@
   </si>
   <si>
     <t>getAvatarFrame</t>
-  </si>
-  <si>
-    <t>1_3</t>
   </si>
   <si>
     <t>1990000_2000000</t>
@@ -129,7 +84,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,17 +252,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -760,7 +704,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -775,9 +719,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1118,21 +1059,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.5" style="2" customWidth="1"/>
-    <col min="7" max="8" width="9" style="2"/>
-    <col min="9" max="9" width="9.25" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="2" customWidth="1"/>
+    <col min="6" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1148,93 +1088,79 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:5">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
-      <c r="A5" s="5">
+    <row r="5" s="1" customFormat="1" spans="1:5">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="1">
         <v>99</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="9:9">
-      <c r="I6"/>
+    <row r="6" spans="8:8">
+      <c r="H6"/>
     </row>
-    <row r="7" spans="9:9">
-      <c r="I7"/>
+    <row r="7" spans="8:8">
+      <c r="H7"/>
     </row>
-    <row r="8" spans="9:9">
-      <c r="I8"/>
+    <row r="8" spans="8:8">
+      <c r="H8"/>
     </row>
-    <row r="9" spans="9:9">
-      <c r="I9"/>
+    <row r="9" spans="8:8">
+      <c r="H9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -26,12 +26,72 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+仅显示用，原价值(金币)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+仅显示用，超值 X%</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>序列ID</t>
   </si>
   <si>
+    <t>原价值</t>
+  </si>
+  <si>
+    <t>超值</t>
+  </si>
+  <si>
     <t>购买金额</t>
   </si>
   <si>
@@ -51,6 +111,12 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>wasPrice</t>
+  </si>
+  <si>
+    <t>bestValue</t>
   </si>
   <si>
     <t>money</t>
@@ -84,7 +150,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +318,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1059,20 +1136,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="22.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1088,79 +1167,106 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="E3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:5">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="C5" s="1">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
         <v>99</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" spans="8:8">
-      <c r="H6"/>
+    <row r="6" spans="10:10">
+      <c r="J6"/>
     </row>
-    <row r="7" spans="8:8">
-      <c r="H7"/>
+    <row r="7" spans="10:10">
+      <c r="J7"/>
     </row>
-    <row r="8" spans="8:8">
-      <c r="H8"/>
+    <row r="8" spans="10:10">
+      <c r="J8"/>
     </row>
-    <row r="9" spans="8:8">
-      <c r="H9"/>
+    <row r="9" spans="10:10">
+      <c r="J9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -107,7 +107,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -131,10 +131,10 @@
     <t>getAvatarFrame</t>
   </si>
   <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1022502_5;1022501_3</t>
+    <t>1990000_3465000</t>
+  </si>
+  <si>
+    <t>1022501_3|1022502_5</t>
   </si>
   <si>
     <t>1031351_1</t>
@@ -320,12 +320,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1234,10 +1234,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>1000000</v>
+        <v>99000</v>
       </c>
       <c r="C5" s="1">
-        <v>100</v>
+        <v>3500</v>
       </c>
       <c r="D5" s="1">
         <v>99</v>

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8896BD91-8030-4945-9EE7-638B417CCC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="firstpayment" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,6 +107,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
@@ -144,17 +141,19 @@
   </si>
   <si>
     <t>1031351_1</t>
-  </si>
-  <si>
-    <t>BigDecimal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,10 +173,162 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -190,21 +341,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,12 +351,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -226,9 +550,266 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -236,7 +817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -245,24 +826,68 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -540,19 +1165,17 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.75" style="2" customWidth="1"/>
+    <col min="2" max="4" width="18.75" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
@@ -561,7 +1184,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -584,53 +1207,53 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="G3" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -639,7 +1262,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -653,30 +1276,30 @@
         <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="10:10">
       <c r="J6"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="10:10">
       <c r="J7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="10:10">
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="10:10">
       <c r="J9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>序列ID</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
   </si>
   <si>
     <t>map&lt;int{_}long&gt;{|}</t>
@@ -150,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +171,14 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -331,7 +342,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,6 +357,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -525,12 +542,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -651,55 +683,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,74 +743,77 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -794,7 +826,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1140,9 +1175,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="2" customWidth="1"/>
+    <col min="2" max="4" width="18.75" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
@@ -1179,45 +1212,45 @@
         <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>8</v>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1243,13 +1276,13 @@
         <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="10:10">

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -76,12 +76,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>序列ID</t>
   </si>
@@ -104,6 +127,9 @@
     <t>头像框奖励</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -113,6 +139,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -134,6 +163,9 @@
     <t>getAvatarFrame</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>1990000_3465000</t>
   </si>
   <si>
@@ -141,6 +173,9 @@
   </si>
   <si>
     <t>1031351_1</t>
+  </si>
+  <si>
+    <t>1_google99|2_ios99</t>
   </si>
 </sst>
 </file>
@@ -817,7 +852,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -829,7 +864,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1179,12 +1214,13 @@
     <col min="5" max="5" width="19.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
-    <col min="8" max="9" width="9" style="2"/>
+    <col min="8" max="8" width="21" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
     <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1206,51 +1242,60 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1262,7 +1307,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1273,16 +1318,19 @@
         <v>3500</v>
       </c>
       <c r="D5" s="1">
-        <v>99</v>
+        <v>0.99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="10:10">

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7228D867-4887-4757-B85D-BC0E7F5FA754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="firstpayment" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -82,12 +76,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>序列ID</t>
   </si>
@@ -110,6 +127,9 @@
     <t>头像框奖励</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -119,6 +139,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -140,6 +163,9 @@
     <t>getAvatarFrame</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>1990000_3465000</t>
   </si>
   <si>
@@ -149,31 +175,20 @@
     <t>1031351_1</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{|}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>map&lt;int{_}String&gt;{|}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>渠道商品ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>channelCommodity</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1_1|2_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t>1_google99|2_ios99</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +220,150 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -217,34 +376,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,7 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,8 +396,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -287,13 +600,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -312,27 +867,62 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -610,27 +1200,27 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
     <col min="2" max="4" width="18.75" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" style="2" customWidth="1"/>
     <col min="9" max="9" width="9" style="2"/>
     <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -652,63 +1242,63 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -717,7 +1307,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -728,36 +1318,36 @@
         <v>3500</v>
       </c>
       <c r="D5" s="1">
-        <v>99</v>
+        <v>0.99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="10:10">
       <c r="J6"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="10:10">
       <c r="J7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="10:10">
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="10:10">
       <c r="J9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -166,7 +166,7 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_3465000</t>
+    <t>1990000_24255000</t>
   </si>
   <si>
     <t>1022501_3|1022502_5</t>
@@ -366,12 +366,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1220,7 +1220,7 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1307,7 +1307,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1333,16 +1333,16 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="10:10">
+    <row r="6" spans="1:10">
       <c r="J6"/>
     </row>
-    <row r="7" spans="10:10">
+    <row r="7" spans="1:10">
       <c r="J7"/>
     </row>
-    <row r="8" spans="10:10">
+    <row r="8" spans="1:10">
       <c r="J8"/>
     </row>
-    <row r="9" spans="10:10">
+    <row r="9" spans="1:10">
       <c r="J9"/>
     </row>
   </sheetData>

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="firstpayment" sheetId="1" r:id="rId1"/>
@@ -366,12 +366,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>99000</v>
+        <v>693000</v>
       </c>
       <c r="C5" s="1">
         <v>3500</v>

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -166,10 +166,10 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_24255000</t>
-  </si>
-  <si>
-    <t>1022501_3|1022502_5</t>
+    <t>1990000_107000</t>
+  </si>
+  <si>
+    <t>1022502_2|1022501_50</t>
   </si>
   <si>
     <t>1031351_1</t>
@@ -366,12 +366,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1312,10 +1312,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>693000</v>
+        <v>29700</v>
       </c>
       <c r="C5" s="1">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="D5" s="1">
         <v>0.99</v>

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="firstpayment" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_107000</t>
+    <t>1990000_162000</t>
   </si>
   <si>
     <t>1022502_2|1022501_50</t>
@@ -366,12 +366,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="firstpayment" sheetId="1" r:id="rId1"/>
@@ -166,10 +166,10 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_162000</t>
-  </si>
-  <si>
-    <t>1022502_2|1022501_50</t>
+    <t>1990000_24255000</t>
+  </si>
+  <si>
+    <t>1022501_3|1022502_5</t>
   </si>
   <si>
     <t>1031351_1</t>
@@ -1312,10 +1312,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>29700</v>
+        <v>693000</v>
       </c>
       <c r="C5" s="1">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="D5" s="1">
         <v>0.99</v>

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="firstpayment" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_162000</t>
+    <t>1990000_1318000</t>
   </si>
   <si>
     <t>1022502_2|1022501_50</t>
@@ -366,12 +366,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1315,7 +1315,7 @@
         <v>29700</v>
       </c>
       <c r="C5" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="D5" s="1">
         <v>0.99</v>

--- a/slots/resources/sample/FirstPayment.xlsx
+++ b/slots/resources/sample/FirstPayment.xlsx
@@ -166,10 +166,10 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_24255000</t>
-  </si>
-  <si>
-    <t>1022501_3|1022502_5</t>
+    <t>1990000_1318000</t>
+  </si>
+  <si>
+    <t>1022502_2|1022501_50</t>
   </si>
   <si>
     <t>1031351_1</t>
@@ -366,12 +366,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1312,10 +1312,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>693000</v>
+        <v>29700</v>
       </c>
       <c r="C5" s="1">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="D5" s="1">
         <v>0.99</v>
